--- a/CO国試data/CO_questions_2024.xlsx
+++ b/CO国試data/CO_questions_2024.xlsx
@@ -545,12 +545,12 @@
           <t>疾病と障害の成り立ち及び回復過程の促進</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>病態の基礎</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>1</v>
       </c>
@@ -599,7 +599,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
           <t>False</t>
@@ -635,15 +634,15 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>視覚情報処理過程の概要</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>1</v>
       </c>
@@ -692,7 +691,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
           <t>False</t>
@@ -728,15 +726,15 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>視覚情報処理過程の概要</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>3</v>
       </c>
@@ -785,7 +783,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
           <t>True</t>
@@ -821,15 +818,15 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>1</v>
       </c>
@@ -878,7 +875,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
           <t>False</t>
@@ -914,15 +910,15 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>3</v>
       </c>
@@ -971,7 +967,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
           <t>True</t>
@@ -1007,15 +1002,15 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>1</v>
       </c>
@@ -1064,7 +1059,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
           <t>False</t>
@@ -1103,12 +1097,12 @@
           <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>保健、医療、福祉、介護の推進</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>3</v>
       </c>
@@ -1157,7 +1151,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
           <t>True</t>
@@ -1196,12 +1189,12 @@
           <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>視能訓練士の役割と義務</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>1</v>
       </c>
@@ -1250,7 +1243,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
           <t>False</t>
@@ -1286,15 +1278,15 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達・加齢</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
+          <t>人体の構造と機能及び心身の発達</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>運動器</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>3</v>
       </c>
@@ -1343,7 +1335,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
           <t>True</t>
@@ -1379,15 +1370,15 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達・加齢</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
+          <t>人体の構造と機能及び心身の発達</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>脳・神経</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>1</v>
       </c>
@@ -1436,7 +1427,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
           <t>False</t>
@@ -1472,15 +1462,15 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>2</v>
       </c>
@@ -1570,15 +1560,15 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>1</v>
       </c>
@@ -1627,7 +1617,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
           <t>False</t>
@@ -1663,15 +1652,15 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
         <v>4</v>
       </c>
@@ -1721,7 +1710,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
           <t>False</t>
@@ -1757,15 +1745,15 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>2</v>
       </c>
@@ -1855,15 +1843,15 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
         <v>3</v>
       </c>
@@ -1912,7 +1900,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
           <t>False</t>
@@ -1948,15 +1935,15 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達・加齢</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
+          <t>人体の構造と機能及び心身の発達</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>脳・神経</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
         <v>1</v>
       </c>
@@ -2005,7 +1992,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
           <t>False</t>
@@ -2041,15 +2027,15 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
         <v>3</v>
       </c>
@@ -2099,7 +2085,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
           <t>False</t>
@@ -2135,15 +2120,15 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t>両眼視機能と眼球運動</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>両眼視機能と眼球運動</t>
-        </is>
-      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
         <v>3</v>
       </c>
@@ -2236,12 +2221,12 @@
           <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>視能訓練士の役割と義務</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
         <v>1</v>
       </c>
@@ -2290,7 +2275,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
           <t>False</t>
@@ -2326,15 +2310,15 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ロービジョン</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
         <is>
           <t>視能矯正訓練の対象となる視能障害</t>
         </is>
       </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
         <v>1</v>
       </c>
@@ -2383,7 +2367,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
           <t>False</t>
@@ -2419,15 +2402,15 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
         <v>1</v>
       </c>
@@ -2476,7 +2459,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
           <t>False</t>
@@ -2512,15 +2494,15 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
         <v>3</v>
       </c>
@@ -2570,7 +2552,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr">
         <is>
           <t>False</t>
@@ -2606,15 +2587,15 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
         <v>3</v>
       </c>
@@ -2663,7 +2644,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
           <t>True</t>
@@ -2699,15 +2679,15 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
         <v>1</v>
       </c>
@@ -2756,7 +2736,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr">
         <is>
           <t>False</t>
@@ -2792,15 +2771,15 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
         <v>3</v>
       </c>
@@ -2849,7 +2828,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr">
         <is>
           <t>True</t>
@@ -2885,15 +2863,15 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
           <t>視能矯正の枠組み</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>視能矯正の枠組み</t>
-        </is>
-      </c>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
         <v>2</v>
       </c>
@@ -2942,7 +2920,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr">
         <is>
           <t>False</t>
@@ -2978,15 +2955,15 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
         <v>2</v>
       </c>
@@ -3036,7 +3013,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr">
         <is>
           <t>False</t>
@@ -3072,15 +3048,15 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
           <t>視能矯正の枠組み</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>視能矯正の枠組み</t>
-        </is>
-      </c>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
         <v>2</v>
       </c>
@@ -3129,7 +3105,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr">
         <is>
           <t>False</t>
@@ -3165,15 +3140,15 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
         <v>2</v>
       </c>
@@ -3223,7 +3198,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr">
         <is>
           <t>False</t>
@@ -3259,15 +3233,15 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
         <v>1</v>
       </c>
@@ -3316,7 +3290,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr">
         <is>
           <t>False</t>
@@ -3352,15 +3325,15 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
         <v>3</v>
       </c>
@@ -3450,15 +3423,15 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
         <v>2</v>
       </c>
@@ -3507,7 +3480,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr">
         <is>
           <t>False</t>
@@ -3543,15 +3515,15 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
           <t>両眼視機能と眼球運動</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>両眼視機能と眼球運動</t>
-        </is>
-      </c>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
         <v>3</v>
       </c>
@@ -3600,7 +3572,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr">
         <is>
           <t>True</t>
@@ -3636,15 +3607,15 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
         <v>2</v>
       </c>
@@ -3734,15 +3705,15 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
         <v>1</v>
       </c>
@@ -3791,7 +3762,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr">
         <is>
           <t>False</t>
@@ -3827,15 +3797,15 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
         <v>3</v>
       </c>
@@ -3886,7 +3856,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr">
         <is>
           <t>False</t>
@@ -3922,15 +3891,15 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
         <is>
           <t>生体と検査機器</t>
         </is>
       </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
         <v>2</v>
       </c>
@@ -3979,7 +3948,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr">
         <is>
           <t>False</t>
@@ -4015,15 +3983,15 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
         <v>1</v>
       </c>
@@ -4072,7 +4040,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr">
         <is>
           <t>False</t>
@@ -4108,15 +4075,15 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
         <v>1</v>
       </c>
@@ -4165,7 +4132,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr">
         <is>
           <t>False</t>
@@ -4201,15 +4167,15 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="n">
         <v>1</v>
       </c>
@@ -4258,7 +4224,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr">
         <is>
           <t>False</t>
@@ -4294,15 +4259,15 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" t="n">
         <v>3</v>
       </c>
@@ -4351,7 +4316,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr">
         <is>
           <t>True</t>
@@ -4387,15 +4351,15 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
         <v>2</v>
       </c>
@@ -4444,7 +4408,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr">
         <is>
           <t>False</t>
@@ -4483,12 +4446,12 @@
           <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>公衆衛生学</t>
         </is>
       </c>
+      <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
         <v>1</v>
       </c>
@@ -4537,7 +4500,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr">
         <is>
           <t>False</t>
@@ -4573,15 +4535,15 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
         <v>1</v>
       </c>
@@ -4630,7 +4592,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R45" t="inlineStr"/>
       <c r="S45" t="inlineStr">
         <is>
           <t>False</t>
@@ -4666,15 +4627,15 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
         <v>1</v>
       </c>
@@ -4723,7 +4684,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr">
         <is>
           <t>False</t>
@@ -4762,12 +4722,12 @@
           <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>視能訓練士の役割と義務</t>
         </is>
       </c>
+      <c r="G47" t="inlineStr"/>
       <c r="H47" t="n">
         <v>2</v>
       </c>
@@ -4816,7 +4776,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr">
         <is>
           <t>False</t>
@@ -4852,15 +4811,15 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
         <v>1</v>
       </c>
@@ -4909,7 +4868,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R48" t="inlineStr"/>
       <c r="S48" t="inlineStr">
         <is>
           <t>False</t>
@@ -4945,15 +4903,15 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G49" t="inlineStr"/>
       <c r="H49" t="n">
         <v>1</v>
       </c>
@@ -5002,7 +4960,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R49" t="inlineStr"/>
       <c r="S49" t="inlineStr">
         <is>
           <t>False</t>
@@ -5038,15 +4995,15 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G50" t="inlineStr"/>
       <c r="H50" t="n">
         <v>3</v>
       </c>
@@ -5095,7 +5052,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R50" t="inlineStr"/>
       <c r="S50" t="inlineStr">
         <is>
           <t>True</t>
@@ -5131,15 +5087,15 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G51" t="inlineStr"/>
       <c r="H51" t="n">
         <v>1</v>
       </c>
@@ -5188,7 +5144,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R51" t="inlineStr"/>
       <c r="S51" t="inlineStr">
         <is>
           <t>False</t>
@@ -5224,15 +5179,15 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>弱視</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
         <is>
           <t>弱視の基本的知識</t>
         </is>
       </c>
+      <c r="G52" t="inlineStr"/>
       <c r="H52" t="n">
         <v>1</v>
       </c>
@@ -5281,7 +5236,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R52" t="inlineStr"/>
       <c r="S52" t="inlineStr">
         <is>
           <t>False</t>
@@ -5317,15 +5271,15 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G53" t="inlineStr"/>
       <c r="H53" t="n">
         <v>3</v>
       </c>
@@ -5374,7 +5328,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R53" t="inlineStr"/>
       <c r="S53" t="inlineStr">
         <is>
           <t>True</t>
@@ -5410,15 +5363,15 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G54" t="inlineStr"/>
       <c r="H54" t="n">
         <v>1</v>
       </c>
@@ -5467,7 +5420,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R54" t="inlineStr"/>
       <c r="S54" t="inlineStr">
         <is>
           <t>False</t>
@@ -5503,15 +5455,15 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G55" t="inlineStr"/>
       <c r="H55" t="n">
         <v>3</v>
       </c>
@@ -5560,7 +5512,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R55" t="inlineStr"/>
       <c r="S55" t="inlineStr">
         <is>
           <t>True</t>
@@ -5596,15 +5547,15 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G56" t="inlineStr"/>
       <c r="H56" t="n">
         <v>1</v>
       </c>
@@ -5653,7 +5604,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R56" t="inlineStr"/>
       <c r="S56" t="inlineStr">
         <is>
           <t>False</t>
@@ -5689,15 +5639,15 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G57" t="inlineStr"/>
       <c r="H57" t="n">
         <v>1</v>
       </c>
@@ -5746,7 +5696,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R57" t="inlineStr"/>
       <c r="S57" t="inlineStr">
         <is>
           <t>False</t>
@@ -5782,15 +5731,15 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
         <v>2</v>
       </c>
@@ -5839,7 +5788,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R58" t="inlineStr"/>
       <c r="S58" t="inlineStr">
         <is>
           <t>False</t>
@@ -5875,15 +5823,15 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>弱視</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
         <is>
           <t>弱視の基本的知識</t>
         </is>
       </c>
+      <c r="G59" t="inlineStr"/>
       <c r="H59" t="n">
         <v>4</v>
       </c>
@@ -5932,7 +5880,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R59" t="inlineStr"/>
       <c r="S59" t="inlineStr">
         <is>
           <t>True</t>
@@ -5971,12 +5918,12 @@
           <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t>視能訓練士の役割と義務</t>
         </is>
       </c>
+      <c r="G60" t="inlineStr"/>
       <c r="H60" t="n">
         <v>1</v>
       </c>
@@ -6025,7 +5972,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R60" t="inlineStr"/>
       <c r="S60" t="inlineStr">
         <is>
           <t>False</t>
@@ -6061,15 +6007,15 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>弱視</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
         <is>
           <t>弱視の基本的知識</t>
         </is>
       </c>
+      <c r="G61" t="inlineStr"/>
       <c r="H61" t="n">
         <v>1</v>
       </c>
@@ -6118,7 +6064,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R61" t="inlineStr"/>
       <c r="S61" t="inlineStr">
         <is>
           <t>False</t>
@@ -6154,15 +6099,15 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G62" t="inlineStr"/>
       <c r="H62" t="n">
         <v>1</v>
       </c>
@@ -6211,7 +6156,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr">
         <is>
           <t>False</t>
@@ -6247,15 +6191,15 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G63" t="inlineStr"/>
       <c r="H63" t="n">
         <v>1</v>
       </c>
@@ -6304,7 +6248,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R63" t="inlineStr"/>
       <c r="S63" t="inlineStr">
         <is>
           <t>False</t>
@@ -6340,15 +6283,15 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G64" t="inlineStr"/>
       <c r="H64" t="n">
         <v>3</v>
       </c>
@@ -6397,7 +6340,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R64" t="inlineStr"/>
       <c r="S64" t="inlineStr">
         <is>
           <t>True</t>
@@ -6433,15 +6375,15 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G65" t="inlineStr"/>
       <c r="H65" t="n">
         <v>1</v>
       </c>
@@ -6490,7 +6432,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R65" t="inlineStr"/>
       <c r="S65" t="inlineStr">
         <is>
           <t>False</t>
@@ -6526,15 +6467,15 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>弱視</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
         <is>
           <t>弱視の基本的知識</t>
         </is>
       </c>
+      <c r="G66" t="inlineStr"/>
       <c r="H66" t="n">
         <v>1</v>
       </c>
@@ -6583,7 +6524,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R66" t="inlineStr"/>
       <c r="S66" t="inlineStr">
         <is>
           <t>False</t>
@@ -6619,15 +6559,15 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G67" t="inlineStr"/>
       <c r="H67" t="n">
         <v>2</v>
       </c>
@@ -6717,15 +6657,15 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G68" t="inlineStr"/>
       <c r="H68" t="n">
         <v>2</v>
       </c>
@@ -6775,7 +6715,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R68" t="inlineStr"/>
       <c r="S68" t="inlineStr">
         <is>
           <t>False</t>
@@ -6811,15 +6750,15 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G69" t="inlineStr"/>
       <c r="H69" t="n">
         <v>3</v>
       </c>
@@ -6869,7 +6808,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R69" t="inlineStr"/>
       <c r="S69" t="inlineStr">
         <is>
           <t>False</t>
@@ -6905,15 +6843,15 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G70" t="inlineStr"/>
       <c r="H70" t="n">
         <v>2</v>
       </c>
@@ -6963,7 +6901,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R70" t="inlineStr"/>
       <c r="S70" t="inlineStr">
         <is>
           <t>False</t>
@@ -6999,15 +6936,15 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G71" t="inlineStr"/>
       <c r="H71" t="n">
         <v>4</v>
       </c>
@@ -7097,15 +7034,15 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G72" t="inlineStr"/>
       <c r="H72" t="n">
         <v>4</v>
       </c>
@@ -7195,15 +7132,15 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr"/>
-      <c r="G73" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G73" t="inlineStr"/>
       <c r="H73" t="n">
         <v>4</v>
       </c>
@@ -7293,15 +7230,15 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G74" t="inlineStr"/>
       <c r="H74" t="n">
         <v>4</v>
       </c>
@@ -7391,15 +7328,15 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G75" t="inlineStr"/>
       <c r="H75" t="n">
         <v>4</v>
       </c>
@@ -7489,15 +7426,15 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G76" t="inlineStr"/>
       <c r="H76" t="n">
         <v>2</v>
       </c>
@@ -7547,7 +7484,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R76" t="inlineStr"/>
       <c r="S76" t="inlineStr">
         <is>
           <t>False</t>
@@ -7583,15 +7519,15 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達・加齢</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr"/>
-      <c r="G77" t="inlineStr">
+          <t>人体の構造と機能及び心身の発達</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
         <is>
           <t>心身の成長・発達、加齢</t>
         </is>
       </c>
+      <c r="G77" t="inlineStr"/>
       <c r="H77" t="n">
         <v>1</v>
       </c>
@@ -7640,7 +7576,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R77" t="inlineStr"/>
       <c r="S77" t="inlineStr">
         <is>
           <t>False</t>
@@ -7676,15 +7611,15 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達・加齢</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr">
+          <t>人体の構造と機能及び心身の発達</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
         <is>
           <t>脳・神経</t>
         </is>
       </c>
+      <c r="G78" t="inlineStr"/>
       <c r="H78" t="n">
         <v>1</v>
       </c>
@@ -7733,7 +7668,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R78" t="inlineStr"/>
       <c r="S78" t="inlineStr">
         <is>
           <t>False</t>
@@ -7769,15 +7703,15 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達・加齢</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr"/>
-      <c r="G79" t="inlineStr">
+          <t>人体の構造と機能及び心身の発達</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
         <is>
           <t>心臓、血管</t>
         </is>
       </c>
+      <c r="G79" t="inlineStr"/>
       <c r="H79" t="n">
         <v>1</v>
       </c>
@@ -7826,7 +7760,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R79" t="inlineStr"/>
       <c r="S79" t="inlineStr">
         <is>
           <t>False</t>
@@ -7862,15 +7795,15 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
         <is>
           <t>視覚情報処理過程の概要</t>
         </is>
       </c>
+      <c r="G80" t="inlineStr"/>
       <c r="H80" t="n">
         <v>1</v>
       </c>
@@ -7919,7 +7852,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R80" t="inlineStr"/>
       <c r="S80" t="inlineStr">
         <is>
           <t>False</t>
@@ -7955,15 +7887,15 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達・加齢</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr">
+          <t>人体の構造と機能及び心身の発達</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
         <is>
           <t>心身の成長・発達、加齢</t>
         </is>
       </c>
+      <c r="G81" t="inlineStr"/>
       <c r="H81" t="n">
         <v>1</v>
       </c>
@@ -8012,7 +7944,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R81" t="inlineStr"/>
       <c r="S81" t="inlineStr">
         <is>
           <t>False</t>
@@ -8048,15 +7979,15 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
         <is>
           <t>生体と検査機器</t>
         </is>
       </c>
+      <c r="G82" t="inlineStr"/>
       <c r="H82" t="n">
         <v>1</v>
       </c>
@@ -8105,7 +8036,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R82" t="inlineStr"/>
       <c r="S82" t="inlineStr">
         <is>
           <t>False</t>
@@ -8141,15 +8071,15 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G83" t="inlineStr"/>
       <c r="H83" t="n">
         <v>3</v>
       </c>
@@ -8198,7 +8128,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R83" t="inlineStr"/>
       <c r="S83" t="inlineStr">
         <is>
           <t>True</t>
@@ -8237,12 +8166,12 @@
           <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr">
+      <c r="F84" t="inlineStr">
         <is>
           <t>保健、医療、福祉、介護の推進</t>
         </is>
       </c>
+      <c r="G84" t="inlineStr"/>
       <c r="H84" t="n">
         <v>1</v>
       </c>
@@ -8291,7 +8220,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R84" t="inlineStr"/>
       <c r="S84" t="inlineStr">
         <is>
           <t>False</t>
@@ -8327,15 +8255,15 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr"/>
-      <c r="G85" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
         <is>
           <t>生体と検査機器</t>
         </is>
       </c>
+      <c r="G85" t="inlineStr"/>
       <c r="H85" t="n">
         <v>1</v>
       </c>
@@ -8384,7 +8312,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R85" t="inlineStr"/>
       <c r="S85" t="inlineStr">
         <is>
           <t>False</t>
@@ -8420,15 +8347,15 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>眼科薬理学</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
         <is>
           <t>眼薬理学</t>
         </is>
       </c>
+      <c r="G86" t="inlineStr"/>
       <c r="H86" t="n">
         <v>1</v>
       </c>
@@ -8477,7 +8404,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R86" t="inlineStr"/>
       <c r="S86" t="inlineStr">
         <is>
           <t>False</t>
@@ -8513,15 +8439,15 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
           <t>両眼視機能と眼球運動</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr"/>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>両眼視機能と眼球運動</t>
-        </is>
-      </c>
+      <c r="G87" t="inlineStr"/>
       <c r="H87" t="n">
         <v>2</v>
       </c>
@@ -8611,15 +8537,15 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G88" t="inlineStr"/>
       <c r="H88" t="n">
         <v>1</v>
       </c>
@@ -8668,7 +8594,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R88" t="inlineStr"/>
       <c r="S88" t="inlineStr">
         <is>
           <t>False</t>
@@ -8704,15 +8629,15 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G89" t="inlineStr"/>
       <c r="H89" t="n">
         <v>1</v>
       </c>
@@ -8761,7 +8686,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R89" t="inlineStr"/>
       <c r="S89" t="inlineStr">
         <is>
           <t>False</t>
@@ -8797,15 +8721,15 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
         <is>
           <t>生体と検査機器</t>
         </is>
       </c>
+      <c r="G90" t="inlineStr"/>
       <c r="H90" t="n">
         <v>3</v>
       </c>
@@ -8854,7 +8778,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R90" t="inlineStr"/>
       <c r="S90" t="inlineStr">
         <is>
           <t>True</t>
@@ -8890,15 +8813,15 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
           <t>両眼視機能と眼球運動</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>両眼視機能と眼球運動</t>
-        </is>
-      </c>
+      <c r="G91" t="inlineStr"/>
       <c r="H91" t="n">
         <v>1</v>
       </c>
@@ -8947,7 +8870,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R91" t="inlineStr"/>
       <c r="S91" t="inlineStr">
         <is>
           <t>False</t>
@@ -8983,15 +8905,15 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
           <t>両眼視機能と眼球運動</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>両眼視機能と眼球運動</t>
-        </is>
-      </c>
+      <c r="G92" t="inlineStr"/>
       <c r="H92" t="n">
         <v>1</v>
       </c>
@@ -9040,7 +8962,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R92" t="inlineStr"/>
       <c r="S92" t="inlineStr">
         <is>
           <t>False</t>
@@ -9076,15 +8997,15 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
           <t>両眼視機能と眼球運動</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>両眼視機能と眼球運動</t>
-        </is>
-      </c>
+      <c r="G93" t="inlineStr"/>
       <c r="H93" t="n">
         <v>1</v>
       </c>
@@ -9133,7 +9054,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R93" t="inlineStr"/>
       <c r="S93" t="inlineStr">
         <is>
           <t>False</t>
@@ -9169,15 +9089,15 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G94" t="inlineStr"/>
       <c r="H94" t="n">
         <v>2</v>
       </c>
@@ -9267,15 +9187,15 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
           <t>両眼視機能と眼球運動</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>両眼視機能と眼球運動</t>
-        </is>
-      </c>
+      <c r="G95" t="inlineStr"/>
       <c r="H95" t="n">
         <v>2</v>
       </c>
@@ -9324,7 +9244,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R95" t="inlineStr"/>
       <c r="S95" t="inlineStr">
         <is>
           <t>False</t>
@@ -9360,15 +9279,15 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
           <t>両眼視機能と眼球運動</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>両眼視機能と眼球運動</t>
-        </is>
-      </c>
+      <c r="G96" t="inlineStr"/>
       <c r="H96" t="n">
         <v>3</v>
       </c>
@@ -9417,7 +9336,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R96" t="inlineStr"/>
       <c r="S96" t="inlineStr">
         <is>
           <t>True</t>
@@ -9453,15 +9371,15 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G97" t="inlineStr"/>
       <c r="H97" t="n">
         <v>2</v>
       </c>
@@ -9510,7 +9428,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R97" t="inlineStr"/>
       <c r="S97" t="inlineStr">
         <is>
           <t>False</t>
@@ -9546,15 +9463,15 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
           <t>両眼視機能と眼球運動</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>両眼視機能と眼球運動</t>
-        </is>
-      </c>
+      <c r="G98" t="inlineStr"/>
       <c r="H98" t="n">
         <v>1</v>
       </c>
@@ -9603,7 +9520,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R98" t="inlineStr"/>
       <c r="S98" t="inlineStr">
         <is>
           <t>False</t>
@@ -9639,15 +9555,15 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>臨床心理</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr"/>
-      <c r="G99" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
         <is>
           <t>視能矯正訓練の臨床心理概要</t>
         </is>
       </c>
+      <c r="G99" t="inlineStr"/>
       <c r="H99" t="n">
         <v>2</v>
       </c>
@@ -9696,7 +9612,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R99" t="inlineStr"/>
       <c r="S99" t="inlineStr">
         <is>
           <t>False</t>
@@ -9732,15 +9647,15 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G100" t="inlineStr"/>
       <c r="H100" t="n">
         <v>2</v>
       </c>
@@ -9789,7 +9704,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R100" t="inlineStr"/>
       <c r="S100" t="inlineStr">
         <is>
           <t>False</t>
@@ -9825,15 +9739,15 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr"/>
-      <c r="G101" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G101" t="inlineStr"/>
       <c r="H101" t="n">
         <v>2</v>
       </c>
@@ -9923,15 +9837,15 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G102" t="inlineStr"/>
       <c r="H102" t="n">
         <v>1</v>
       </c>
@@ -9980,7 +9894,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R102" t="inlineStr"/>
       <c r="S102" t="inlineStr">
         <is>
           <t>False</t>
@@ -10016,15 +9929,15 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr"/>
-      <c r="G103" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G103" t="inlineStr"/>
       <c r="H103" t="n">
         <v>2</v>
       </c>
@@ -10114,15 +10027,15 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G104" t="inlineStr"/>
       <c r="H104" t="n">
         <v>3</v>
       </c>
@@ -10212,15 +10125,15 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G105" t="inlineStr"/>
       <c r="H105" t="n">
         <v>2</v>
       </c>
@@ -10269,7 +10182,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R105" t="inlineStr"/>
       <c r="S105" t="inlineStr">
         <is>
           <t>False</t>
@@ -10305,15 +10217,15 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G106" t="inlineStr"/>
       <c r="H106" t="n">
         <v>1</v>
       </c>
@@ -10362,7 +10274,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R106" t="inlineStr"/>
       <c r="S106" t="inlineStr">
         <is>
           <t>False</t>
@@ -10398,15 +10309,15 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>弱視</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr"/>
-      <c r="G107" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
         <is>
           <t>弱視の基本的知識</t>
         </is>
       </c>
+      <c r="G107" t="inlineStr"/>
       <c r="H107" t="n">
         <v>1</v>
       </c>
@@ -10455,7 +10366,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R107" t="inlineStr"/>
       <c r="S107" t="inlineStr">
         <is>
           <t>False</t>
@@ -10491,15 +10401,15 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr"/>
-      <c r="G108" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G108" t="inlineStr"/>
       <c r="H108" t="n">
         <v>1</v>
       </c>
@@ -10548,7 +10458,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R108" t="inlineStr"/>
       <c r="S108" t="inlineStr">
         <is>
           <t>False</t>
@@ -10584,15 +10493,15 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G109" t="inlineStr"/>
       <c r="H109" t="n">
         <v>1</v>
       </c>
@@ -10641,7 +10550,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R109" t="inlineStr"/>
       <c r="S109" t="inlineStr">
         <is>
           <t>False</t>
@@ -10677,15 +10585,15 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G110" t="inlineStr"/>
       <c r="H110" t="n">
         <v>1</v>
       </c>
@@ -10734,7 +10642,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R110" t="inlineStr"/>
       <c r="S110" t="inlineStr">
         <is>
           <t>False</t>
@@ -10770,15 +10677,15 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr"/>
-      <c r="G111" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G111" t="inlineStr"/>
       <c r="H111" t="n">
         <v>2</v>
       </c>
@@ -10827,7 +10734,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R111" t="inlineStr"/>
       <c r="S111" t="inlineStr">
         <is>
           <t>False</t>
@@ -10863,15 +10769,15 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G112" t="inlineStr"/>
       <c r="H112" t="n">
         <v>2</v>
       </c>
@@ -10961,15 +10867,15 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr"/>
-      <c r="G113" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G113" t="inlineStr"/>
       <c r="H113" t="n">
         <v>1</v>
       </c>
@@ -11018,7 +10924,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R113" t="inlineStr"/>
       <c r="S113" t="inlineStr">
         <is>
           <t>False</t>
@@ -11054,15 +10959,15 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr"/>
-      <c r="G114" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G114" t="inlineStr"/>
       <c r="H114" t="n">
         <v>1</v>
       </c>
@@ -11111,7 +11016,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R114" t="inlineStr"/>
       <c r="S114" t="inlineStr">
         <is>
           <t>False</t>
@@ -11147,15 +11051,15 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr"/>
-      <c r="G115" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G115" t="inlineStr"/>
       <c r="H115" t="n">
         <v>2</v>
       </c>
@@ -11204,7 +11108,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R115" t="inlineStr"/>
       <c r="S115" t="inlineStr">
         <is>
           <t>False</t>
@@ -11240,15 +11143,15 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
           <t>両眼視機能と眼球運動</t>
         </is>
       </c>
-      <c r="F116" t="inlineStr"/>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>両眼視機能と眼球運動</t>
-        </is>
-      </c>
+      <c r="G116" t="inlineStr"/>
       <c r="H116" t="n">
         <v>3</v>
       </c>
@@ -11297,7 +11200,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R116" t="inlineStr"/>
       <c r="S116" t="inlineStr">
         <is>
           <t>True</t>
@@ -11333,15 +11235,15 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr"/>
-      <c r="G117" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G117" t="inlineStr"/>
       <c r="H117" t="n">
         <v>1</v>
       </c>
@@ -11390,7 +11292,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R117" t="inlineStr"/>
       <c r="S117" t="inlineStr">
         <is>
           <t>False</t>
@@ -11426,15 +11327,15 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr"/>
-      <c r="G118" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G118" t="inlineStr"/>
       <c r="H118" t="n">
         <v>3</v>
       </c>
@@ -11483,7 +11384,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R118" t="inlineStr"/>
       <c r="S118" t="inlineStr">
         <is>
           <t>True</t>
@@ -11519,15 +11419,15 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr"/>
-      <c r="G119" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G119" t="inlineStr"/>
       <c r="H119" t="n">
         <v>1</v>
       </c>
@@ -11576,7 +11476,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R119" t="inlineStr"/>
       <c r="S119" t="inlineStr">
         <is>
           <t>False</t>
@@ -11612,15 +11511,15 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr"/>
-      <c r="G120" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G120" t="inlineStr"/>
       <c r="H120" t="n">
         <v>3</v>
       </c>
@@ -11669,7 +11568,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R120" t="inlineStr"/>
       <c r="S120" t="inlineStr">
         <is>
           <t>True</t>
@@ -11705,15 +11603,15 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr"/>
-      <c r="G121" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G121" t="inlineStr"/>
       <c r="H121" t="n">
         <v>1</v>
       </c>
@@ -11762,7 +11660,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R121" t="inlineStr"/>
       <c r="S121" t="inlineStr">
         <is>
           <t>False</t>
@@ -11798,15 +11695,15 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr"/>
-      <c r="G122" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G122" t="inlineStr"/>
       <c r="H122" t="n">
         <v>1</v>
       </c>
@@ -11855,7 +11752,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R122" t="inlineStr"/>
       <c r="S122" t="inlineStr">
         <is>
           <t>False</t>
@@ -11891,15 +11787,15 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr"/>
-      <c r="G123" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G123" t="inlineStr"/>
       <c r="H123" t="n">
         <v>1</v>
       </c>
@@ -11948,7 +11844,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R123" t="inlineStr"/>
       <c r="S123" t="inlineStr">
         <is>
           <t>False</t>
@@ -11984,15 +11879,15 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr"/>
-      <c r="G124" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G124" t="inlineStr"/>
       <c r="H124" t="n">
         <v>1</v>
       </c>
@@ -12041,7 +11936,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R124" t="inlineStr"/>
       <c r="S124" t="inlineStr">
         <is>
           <t>False</t>
@@ -12077,15 +11971,15 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr"/>
-      <c r="G125" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G125" t="inlineStr"/>
       <c r="H125" t="n">
         <v>1</v>
       </c>
@@ -12134,7 +12028,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R125" t="inlineStr"/>
       <c r="S125" t="inlineStr">
         <is>
           <t>False</t>
@@ -12170,15 +12063,15 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr"/>
-      <c r="G126" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G126" t="inlineStr"/>
       <c r="H126" t="n">
         <v>1</v>
       </c>
@@ -12227,7 +12120,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R126" t="inlineStr"/>
       <c r="S126" t="inlineStr">
         <is>
           <t>False</t>
@@ -12263,15 +12155,15 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr"/>
-      <c r="G127" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G127" t="inlineStr"/>
       <c r="H127" t="n">
         <v>3</v>
       </c>
@@ -12320,7 +12212,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R127" t="inlineStr"/>
       <c r="S127" t="inlineStr">
         <is>
           <t>True</t>
@@ -12356,15 +12247,15 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr"/>
-      <c r="G128" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G128" t="inlineStr"/>
       <c r="H128" t="n">
         <v>1</v>
       </c>
@@ -12413,7 +12304,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R128" t="inlineStr"/>
       <c r="S128" t="inlineStr">
         <is>
           <t>False</t>
@@ -12449,15 +12339,15 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr"/>
-      <c r="G129" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G129" t="inlineStr"/>
       <c r="H129" t="n">
         <v>1</v>
       </c>
@@ -12506,7 +12396,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R129" t="inlineStr"/>
       <c r="S129" t="inlineStr">
         <is>
           <t>False</t>
@@ -12542,15 +12431,15 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr"/>
-      <c r="G130" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G130" t="inlineStr"/>
       <c r="H130" t="n">
         <v>1</v>
       </c>
@@ -12599,7 +12488,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R130" t="inlineStr"/>
       <c r="S130" t="inlineStr">
         <is>
           <t>False</t>
@@ -12635,15 +12523,15 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr"/>
-      <c r="G131" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G131" t="inlineStr"/>
       <c r="H131" t="n">
         <v>1</v>
       </c>
@@ -12692,7 +12580,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R131" t="inlineStr"/>
       <c r="S131" t="inlineStr">
         <is>
           <t>False</t>
@@ -12728,15 +12615,15 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr"/>
-      <c r="G132" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G132" t="inlineStr"/>
       <c r="H132" t="n">
         <v>1</v>
       </c>
@@ -12785,7 +12672,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R132" t="inlineStr"/>
       <c r="S132" t="inlineStr">
         <is>
           <t>False</t>
@@ -12821,15 +12707,15 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr"/>
-      <c r="G133" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G133" t="inlineStr"/>
       <c r="H133" t="n">
         <v>2</v>
       </c>
@@ -12878,7 +12764,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R133" t="inlineStr"/>
       <c r="S133" t="inlineStr">
         <is>
           <t>False</t>
@@ -12914,15 +12799,15 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr"/>
-      <c r="G134" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G134" t="inlineStr"/>
       <c r="H134" t="n">
         <v>3</v>
       </c>
@@ -12971,7 +12856,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R134" t="inlineStr"/>
       <c r="S134" t="inlineStr">
         <is>
           <t>True</t>
@@ -13007,15 +12891,15 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr"/>
-      <c r="G135" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G135" t="inlineStr"/>
       <c r="H135" t="n">
         <v>1</v>
       </c>
@@ -13064,7 +12948,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R135" t="inlineStr"/>
       <c r="S135" t="inlineStr">
         <is>
           <t>False</t>
@@ -13100,15 +12983,15 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>弱視</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr"/>
-      <c r="G136" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
         <is>
           <t>弱視の基本的知識</t>
         </is>
       </c>
+      <c r="G136" t="inlineStr"/>
       <c r="H136" t="n">
         <v>3</v>
       </c>
@@ -13157,7 +13040,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R136" t="inlineStr"/>
       <c r="S136" t="inlineStr">
         <is>
           <t>True</t>
@@ -13193,15 +13075,15 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr"/>
-      <c r="G137" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G137" t="inlineStr"/>
       <c r="H137" t="n">
         <v>1</v>
       </c>
@@ -13250,7 +13132,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R137" t="inlineStr"/>
       <c r="S137" t="inlineStr">
         <is>
           <t>False</t>
@@ -13286,15 +13167,15 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>弱視</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr"/>
-      <c r="G138" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
         <is>
           <t>弱視の基本的知識</t>
         </is>
       </c>
+      <c r="G138" t="inlineStr"/>
       <c r="H138" t="n">
         <v>1</v>
       </c>
@@ -13343,7 +13224,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R138" t="inlineStr"/>
       <c r="S138" t="inlineStr">
         <is>
           <t>False</t>
@@ -13379,15 +13259,15 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>弱視</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr"/>
-      <c r="G139" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
         <is>
           <t>弱視の基本的知識</t>
         </is>
       </c>
+      <c r="G139" t="inlineStr"/>
       <c r="H139" t="n">
         <v>2</v>
       </c>
@@ -13436,7 +13316,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R139" t="inlineStr"/>
       <c r="S139" t="inlineStr">
         <is>
           <t>False</t>
@@ -13472,15 +13351,15 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr"/>
-      <c r="G140" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G140" t="inlineStr"/>
       <c r="H140" t="n">
         <v>3</v>
       </c>
@@ -13529,7 +13408,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R140" t="inlineStr"/>
       <c r="S140" t="inlineStr">
         <is>
           <t>True</t>
@@ -13565,15 +13443,15 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr"/>
-      <c r="G141" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G141" t="inlineStr"/>
       <c r="H141" t="n">
         <v>3</v>
       </c>
@@ -13622,7 +13500,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R141" t="inlineStr"/>
       <c r="S141" t="inlineStr">
         <is>
           <t>True</t>
@@ -13658,15 +13535,15 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr"/>
-      <c r="G142" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G142" t="inlineStr"/>
       <c r="H142" t="n">
         <v>4</v>
       </c>
@@ -13756,15 +13633,15 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
           <t>両眼視機能と眼球運動</t>
         </is>
       </c>
-      <c r="F143" t="inlineStr"/>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>両眼視機能と眼球運動</t>
-        </is>
-      </c>
+      <c r="G143" t="inlineStr"/>
       <c r="H143" t="n">
         <v>4</v>
       </c>
@@ -13854,15 +13731,15 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr"/>
-      <c r="G144" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G144" t="inlineStr"/>
       <c r="H144" t="n">
         <v>2</v>
       </c>
@@ -13952,15 +13829,15 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr"/>
-      <c r="G145" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G145" t="inlineStr"/>
       <c r="H145" t="n">
         <v>3</v>
       </c>
@@ -14050,15 +13927,15 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr"/>
-      <c r="G146" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G146" t="inlineStr"/>
       <c r="H146" t="n">
         <v>4</v>
       </c>
@@ -14108,7 +13985,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R146" t="inlineStr"/>
       <c r="S146" t="inlineStr">
         <is>
           <t>False</t>
@@ -14144,15 +14020,15 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr"/>
-      <c r="G147" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G147" t="inlineStr"/>
       <c r="H147" t="n">
         <v>4</v>
       </c>
@@ -14242,15 +14118,15 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr"/>
-      <c r="G148" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G148" t="inlineStr"/>
       <c r="H148" t="n">
         <v>3</v>
       </c>
@@ -14340,15 +14216,15 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr"/>
-      <c r="G149" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G149" t="inlineStr"/>
       <c r="H149" t="n">
         <v>4</v>
       </c>
@@ -14398,7 +14274,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R149" t="inlineStr"/>
       <c r="S149" t="inlineStr">
         <is>
           <t>False</t>
@@ -14434,15 +14309,15 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr"/>
-      <c r="G150" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G150" t="inlineStr"/>
       <c r="H150" t="n">
         <v>4</v>
       </c>
@@ -14532,15 +14407,15 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr"/>
-      <c r="G151" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G151" t="inlineStr"/>
       <c r="H151" t="n">
         <v>3</v>
       </c>
@@ -14590,7 +14465,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R151" t="inlineStr"/>
       <c r="S151" t="inlineStr">
         <is>
           <t>False</t>

--- a/CO国試data/CO_questions_2024.xlsx
+++ b/CO国試data/CO_questions_2024.xlsx
@@ -542,12 +542,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>疾病と障害の成り立ち及び回復過程の促進</t>
+          <t>病態の基礎</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>病態の基礎</t>
+          <t>病因と疾病の種類</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -634,12 +634,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>視覚情報処理過程の概要</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>視覚情報処理過程の概要</t>
+          <t>眼球</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -726,12 +726,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>視覚情報処理過程の概要</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>視覚情報処理過程の概要</t>
+          <t>眼窩</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -818,12 +818,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -910,12 +910,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>画像検査</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>保健、医療、福祉、介護の推進</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>保健、医療、福祉、介護の推進</t>
+          <t>保健、医療、福祉、介護制度</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>視能訓練士の役割と義務</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>視能訓練士の役割と義務</t>
+          <t>医療の質と安全の確保</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達</t>
+          <t>運動器</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>運動器</t>
+          <t>筋の構造と機能</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -1370,12 +1370,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達</t>
+          <t>脳・神経</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>脳・神経</t>
+          <t>自律神経</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -1462,12 +1462,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -1560,12 +1560,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の矯正</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -1652,12 +1652,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>生理光学の基礎知識</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -1745,12 +1745,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>生理光学の基礎知識</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -1843,12 +1843,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>生理光学の基礎知識</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -1935,12 +1935,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達</t>
+          <t>脳・神経</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>脳・神経</t>
+          <t>神経の構造と機能</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -2027,12 +2027,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の矯正</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -2120,12 +2120,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>両眼視機能と眼球運動</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>両眼視機能と眼球運動</t>
+          <t>両眼視</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>視能訓練士の役割と義務</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>視能訓練士の役割と義務</t>
+          <t>医療の質と安全の確保</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
@@ -2310,12 +2310,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の対象となる視能障害</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>視能矯正訓練の対象となる視能障害</t>
+          <t>機能的視能障害</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
@@ -2402,12 +2402,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>屈折検査</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -2494,12 +2494,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>視野検査</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
@@ -2587,12 +2587,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -2771,12 +2771,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>視力検査</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
@@ -2863,12 +2863,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正の枠組み</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>視能矯正の枠組み</t>
+          <t>視能矯正の展開</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
@@ -2955,12 +2955,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>視力検査</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正の枠組み</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>視能矯正の枠組み</t>
+          <t>視能矯正の展開</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
@@ -3140,12 +3140,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
@@ -3233,12 +3233,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の異常</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
@@ -3325,12 +3325,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の矯正</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
@@ -3423,12 +3423,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
@@ -3515,12 +3515,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>両眼視機能と眼球運動</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>両眼視機能と眼球運動</t>
+          <t>外眼筋の作用と眼球運動</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -3607,12 +3607,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
@@ -3705,12 +3705,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>緑内障</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -3891,12 +3891,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>生体と検査機器</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>生体と検査機器</t>
+          <t>視能検査機器の基本的知識</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
@@ -3983,12 +3983,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>涙液検査</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
@@ -4075,12 +4075,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
@@ -4259,12 +4259,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
@@ -4351,12 +4351,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>身体症状症&lt;心因性視能障害&gt;</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
@@ -4443,12 +4443,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>公衆衛生学</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>公衆衛生学</t>
+          <t>公衆衛生総論</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
@@ -4535,12 +4535,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>眼瞼</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
@@ -4719,12 +4719,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>視能訓練士の役割と義務</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>視能訓練士の役割と義務</t>
+          <t>医療の質と安全の確保</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
@@ -4811,12 +4811,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>屈折異常</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
@@ -4903,12 +4903,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>網膜</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
@@ -4995,12 +4995,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
@@ -5087,12 +5087,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
@@ -5179,12 +5179,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>弱視の基本的知識</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>弱視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
@@ -5271,12 +5271,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>眼球運動</t>
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
@@ -5363,12 +5363,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
@@ -5455,12 +5455,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>定義</t>
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
@@ -5547,12 +5547,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G56" t="inlineStr"/>
@@ -5639,12 +5639,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
@@ -5731,12 +5731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
@@ -5823,12 +5823,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>弱視の基本的知識</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>弱視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
@@ -5915,12 +5915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>視能訓練士の役割と義務</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>視能訓練士の役割と義務</t>
+          <t>患者と視能訓練士の関係</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
@@ -6007,12 +6007,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>弱視の基本的知識</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>弱視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G61" t="inlineStr"/>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G62" t="inlineStr"/>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
@@ -6283,12 +6283,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G64" t="inlineStr"/>
@@ -6375,12 +6375,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>眼窩</t>
         </is>
       </c>
       <c r="G65" t="inlineStr"/>
@@ -6467,12 +6467,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>弱視の基本的知識</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>弱視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
@@ -6559,12 +6559,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
@@ -6657,12 +6657,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
@@ -6750,12 +6750,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
@@ -6843,12 +6843,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G70" t="inlineStr"/>
@@ -6936,12 +6936,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>眼底検査</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
@@ -7132,12 +7132,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G73" t="inlineStr"/>
@@ -7230,12 +7230,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G74" t="inlineStr"/>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G75" t="inlineStr"/>
@@ -7426,12 +7426,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G76" t="inlineStr"/>
@@ -7519,12 +7519,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達</t>
+          <t>心身の成長・発達、加齢</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>心身の成長・発達、加齢</t>
+          <t>加齢、老化</t>
         </is>
       </c>
       <c r="G77" t="inlineStr"/>
@@ -7611,12 +7611,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達</t>
+          <t>脳・神経</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>脳・神経</t>
+          <t>末梢神経の構造と機能</t>
         </is>
       </c>
       <c r="G78" t="inlineStr"/>
@@ -7703,12 +7703,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達</t>
+          <t>心臓、血管</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>心臓、血管</t>
+          <t>心臓、血管の構造と機能</t>
         </is>
       </c>
       <c r="G79" t="inlineStr"/>
@@ -7795,12 +7795,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>視覚情報処理過程の概要</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>視覚情報処理過程の概要</t>
+          <t>眼球</t>
         </is>
       </c>
       <c r="G80" t="inlineStr"/>
@@ -7887,12 +7887,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達</t>
+          <t>心身の成長・発達、加齢</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>心身の成長・発達、加齢</t>
+          <t>新生児期、乳児期</t>
         </is>
       </c>
       <c r="G81" t="inlineStr"/>
@@ -7979,12 +7979,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>生体と検査機器</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>生体と検査機器</t>
+          <t>視能検査機器の基本的知識</t>
         </is>
       </c>
       <c r="G82" t="inlineStr"/>
@@ -8071,12 +8071,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G83" t="inlineStr"/>
@@ -8163,12 +8163,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>保健、医療、福祉、介護の推進</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>保健、医療、福祉、介護の推進</t>
+          <t>保健、医療、福祉、介護制度</t>
         </is>
       </c>
       <c r="G84" t="inlineStr"/>
@@ -8255,12 +8255,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>生体と検査機器</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>生体と検査機器</t>
+          <t>視能検査機器の基本的知識</t>
         </is>
       </c>
       <c r="G85" t="inlineStr"/>
@@ -8347,12 +8347,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>眼薬理学</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>眼薬理学</t>
+          <t>薬物の副作用</t>
         </is>
       </c>
       <c r="G86" t="inlineStr"/>
@@ -8439,12 +8439,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>両眼視機能と眼球運動</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>両眼視機能と眼球運動</t>
+          <t>両眼視</t>
         </is>
       </c>
       <c r="G87" t="inlineStr"/>
@@ -8537,12 +8537,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G88" t="inlineStr"/>
@@ -8629,12 +8629,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G89" t="inlineStr"/>
@@ -8721,12 +8721,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>生体と検査機器</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>生体と検査機器</t>
+          <t>視能検査機器の基本的知識</t>
         </is>
       </c>
       <c r="G90" t="inlineStr"/>
@@ -8813,12 +8813,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>両眼視機能と眼球運動</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>両眼視機能と眼球運動</t>
+          <t>外眼筋の作用と眼球運動</t>
         </is>
       </c>
       <c r="G91" t="inlineStr"/>
@@ -8905,12 +8905,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>両眼視機能と眼球運動</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>両眼視機能と眼球運動</t>
+          <t>外眼筋の作用と眼球運動</t>
         </is>
       </c>
       <c r="G92" t="inlineStr"/>
@@ -8997,12 +8997,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>両眼視機能と眼球運動</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>両眼視機能と眼球運動</t>
+          <t>両眼視</t>
         </is>
       </c>
       <c r="G93" t="inlineStr"/>
@@ -9089,12 +9089,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G94" t="inlineStr"/>
@@ -9187,12 +9187,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>両眼視機能と眼球運動</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>両眼視機能と眼球運動</t>
+          <t>外眼筋の作用と眼球運動</t>
         </is>
       </c>
       <c r="G95" t="inlineStr"/>
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>両眼視機能と眼球運動</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>両眼視機能と眼球運動</t>
+          <t>輻湊、開散と屈折、調節</t>
         </is>
       </c>
       <c r="G96" t="inlineStr"/>
@@ -9371,12 +9371,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G97" t="inlineStr"/>
@@ -9463,12 +9463,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>両眼視機能と眼球運動</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>両眼視機能と眼球運動</t>
+          <t>外眼筋の作用と眼球運動</t>
         </is>
       </c>
       <c r="G98" t="inlineStr"/>
@@ -9555,12 +9555,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正訓練の臨床心理概要</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>視能矯正訓練の臨床心理概要</t>
+          <t>基本的知識</t>
         </is>
       </c>
       <c r="G99" t="inlineStr"/>
@@ -9647,12 +9647,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>角膜検査</t>
         </is>
       </c>
       <c r="G100" t="inlineStr"/>
@@ -9739,12 +9739,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>視力検査</t>
         </is>
       </c>
       <c r="G101" t="inlineStr"/>
@@ -9837,12 +9837,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>眼圧検査</t>
         </is>
       </c>
       <c r="G102" t="inlineStr"/>
@@ -9929,12 +9929,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>画像検査</t>
         </is>
       </c>
       <c r="G103" t="inlineStr"/>
@@ -10027,12 +10027,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>涙液検査</t>
         </is>
       </c>
       <c r="G104" t="inlineStr"/>
@@ -10125,12 +10125,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>前眼部、透光体検査</t>
         </is>
       </c>
       <c r="G105" t="inlineStr"/>
@@ -10217,12 +10217,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>涙液検査</t>
         </is>
       </c>
       <c r="G106" t="inlineStr"/>
@@ -10309,12 +10309,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>弱視の基本的知識</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>弱視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G107" t="inlineStr"/>
@@ -10401,12 +10401,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G108" t="inlineStr"/>
@@ -10493,12 +10493,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G109" t="inlineStr"/>
@@ -10585,12 +10585,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G110" t="inlineStr"/>
@@ -10677,12 +10677,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の異常</t>
         </is>
       </c>
       <c r="G111" t="inlineStr"/>
@@ -10769,12 +10769,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G112" t="inlineStr"/>
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G113" t="inlineStr"/>
@@ -10959,12 +10959,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G114" t="inlineStr"/>
@@ -11051,12 +11051,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G115" t="inlineStr"/>
@@ -11143,12 +11143,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>両眼視機能と眼球運動</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>両眼視機能と眼球運動</t>
+          <t>輻湊、開散と屈折、調節</t>
         </is>
       </c>
       <c r="G116" t="inlineStr"/>
@@ -11235,12 +11235,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G117" t="inlineStr"/>
@@ -11327,12 +11327,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>ぶどう膜</t>
         </is>
       </c>
       <c r="G118" t="inlineStr"/>
@@ -11419,12 +11419,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G119" t="inlineStr"/>
@@ -11511,12 +11511,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>網膜</t>
         </is>
       </c>
       <c r="G120" t="inlineStr"/>
@@ -11603,12 +11603,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>水晶体</t>
         </is>
       </c>
       <c r="G121" t="inlineStr"/>
@@ -11695,12 +11695,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>強膜</t>
         </is>
       </c>
       <c r="G122" t="inlineStr"/>
@@ -11787,12 +11787,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>角膜</t>
         </is>
       </c>
       <c r="G123" t="inlineStr"/>
@@ -11879,12 +11879,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>結膜</t>
         </is>
       </c>
       <c r="G124" t="inlineStr"/>
@@ -11971,12 +11971,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>水晶体</t>
         </is>
       </c>
       <c r="G125" t="inlineStr"/>
@@ -12063,12 +12063,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>緑内障</t>
         </is>
       </c>
       <c r="G126" t="inlineStr"/>
@@ -12155,12 +12155,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G127" t="inlineStr"/>
@@ -12247,12 +12247,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G128" t="inlineStr"/>
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G129" t="inlineStr"/>
@@ -12431,12 +12431,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G130" t="inlineStr"/>
@@ -12523,12 +12523,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G131" t="inlineStr"/>
@@ -12615,12 +12615,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G132" t="inlineStr"/>
@@ -12707,12 +12707,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G133" t="inlineStr"/>
@@ -12799,12 +12799,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G134" t="inlineStr"/>
@@ -12891,12 +12891,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G135" t="inlineStr"/>
@@ -12983,12 +12983,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>弱視の基本的知識</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>弱視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G136" t="inlineStr"/>
@@ -13075,12 +13075,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G137" t="inlineStr"/>
@@ -13167,12 +13167,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>弱視の基本的知識</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>弱視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G138" t="inlineStr"/>
@@ -13259,12 +13259,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>弱視の基本的知識</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>弱視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G139" t="inlineStr"/>
@@ -13351,12 +13351,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G140" t="inlineStr"/>
@@ -13443,12 +13443,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G141" t="inlineStr"/>
@@ -13535,12 +13535,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>生理光学の基礎知識</t>
         </is>
       </c>
       <c r="G142" t="inlineStr"/>
@@ -13633,12 +13633,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>両眼視機能と眼球運動</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>両眼視機能と眼球運動</t>
+          <t>両眼視</t>
         </is>
       </c>
       <c r="G143" t="inlineStr"/>
@@ -13731,12 +13731,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G144" t="inlineStr"/>
@@ -13829,12 +13829,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G145" t="inlineStr"/>
@@ -13927,12 +13927,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の異常</t>
         </is>
       </c>
       <c r="G146" t="inlineStr"/>
@@ -14020,12 +14020,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>眼窩</t>
         </is>
       </c>
       <c r="G147" t="inlineStr"/>
@@ -14118,12 +14118,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G148" t="inlineStr"/>
@@ -14216,12 +14216,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>定義</t>
         </is>
       </c>
       <c r="G149" t="inlineStr"/>
@@ -14309,12 +14309,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G150" t="inlineStr"/>
@@ -14407,12 +14407,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G151" t="inlineStr"/>

--- a/CO国試data/CO_questions_2024.xlsx
+++ b/CO国試data/CO_questions_2024.xlsx
@@ -550,7 +550,6 @@
           <t>病因と疾病の種類</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>1</v>
       </c>
@@ -642,7 +641,11 @@
           <t>眼球</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ぶどう膜（虹彩、毛様体、脈絡膜）</t>
+        </is>
+      </c>
       <c r="H3" t="n">
         <v>1</v>
       </c>
@@ -734,7 +737,11 @@
           <t>眼窩</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>視神経管</t>
+        </is>
+      </c>
       <c r="H4" t="n">
         <v>3</v>
       </c>
@@ -826,7 +833,11 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>視神経症</t>
+        </is>
+      </c>
       <c r="H5" t="n">
         <v>1</v>
       </c>
@@ -918,7 +929,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>3</v>
       </c>
@@ -1010,7 +1020,11 @@
           <t>画像検査</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>エックス線撮影、CT、MRI</t>
+        </is>
+      </c>
       <c r="H7" t="n">
         <v>1</v>
       </c>
@@ -1102,7 +1116,6 @@
           <t>保健、医療、福祉、介護制度</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>3</v>
       </c>
@@ -1194,7 +1207,6 @@
           <t>医療の質と安全の確保</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>1</v>
       </c>
@@ -1286,7 +1298,11 @@
           <t>筋の構造と機能</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>骨格筋</t>
+        </is>
+      </c>
       <c r="H10" t="n">
         <v>3</v>
       </c>
@@ -1378,7 +1394,11 @@
           <t>自律神経</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>交感神経</t>
+        </is>
+      </c>
       <c r="H11" t="n">
         <v>1</v>
       </c>
@@ -1470,7 +1490,6 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>2</v>
       </c>
@@ -1568,7 +1587,11 @@
           <t>屈折、調節の矯正</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>コンタクトレンズ</t>
+        </is>
+      </c>
       <c r="H13" t="n">
         <v>1</v>
       </c>
@@ -1660,7 +1683,11 @@
           <t>生理光学の基礎知識</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>プリズム</t>
+        </is>
+      </c>
       <c r="H14" t="n">
         <v>4</v>
       </c>
@@ -1753,7 +1780,11 @@
           <t>生理光学の基礎知識</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>レンズ</t>
+        </is>
+      </c>
       <c r="H15" t="n">
         <v>2</v>
       </c>
@@ -1851,7 +1882,11 @@
           <t>生理光学の基礎知識</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>眼球光学系の特徴</t>
+        </is>
+      </c>
       <c r="H16" t="n">
         <v>3</v>
       </c>
@@ -1943,7 +1978,6 @@
           <t>神経の構造と機能</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
         <v>1</v>
       </c>
@@ -2035,7 +2069,11 @@
           <t>屈折、調節の矯正</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>コンタクトレンズ</t>
+        </is>
+      </c>
       <c r="H18" t="n">
         <v>3</v>
       </c>
@@ -2128,7 +2166,11 @@
           <t>両眼視</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Panumの融像感覚圏</t>
+        </is>
+      </c>
       <c r="H19" t="n">
         <v>3</v>
       </c>
@@ -2226,7 +2268,6 @@
           <t>医療の質と安全の確保</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
         <v>1</v>
       </c>
@@ -2318,7 +2359,6 @@
           <t>機能的視能障害</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
         <v>1</v>
       </c>
@@ -2410,7 +2450,11 @@
           <t>屈折検査</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>他覚的屈折検査（波面収差解析を含む）</t>
+        </is>
+      </c>
       <c r="H22" t="n">
         <v>1</v>
       </c>
@@ -2502,7 +2546,11 @@
           <t>視野検査</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>動的、静的視野測定法（自動視野計を含む）</t>
+        </is>
+      </c>
       <c r="H23" t="n">
         <v>3</v>
       </c>
@@ -2595,7 +2643,6 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
         <v>3</v>
       </c>
@@ -2687,7 +2734,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>外斜視</t>
+        </is>
+      </c>
       <c r="H25" t="n">
         <v>1</v>
       </c>
@@ -2779,7 +2830,6 @@
           <t>視力検査</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
         <v>3</v>
       </c>
@@ -2871,7 +2921,6 @@
           <t>視能矯正の展開</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
         <v>2</v>
       </c>
@@ -2963,7 +3012,6 @@
           <t>視力検査</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
         <v>2</v>
       </c>
@@ -3056,7 +3104,11 @@
           <t>視能矯正の展開</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>根拠に基づいた医療〈EBM〉としての視能矯正</t>
+        </is>
+      </c>
       <c r="H29" t="n">
         <v>2</v>
       </c>
@@ -3148,7 +3200,6 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
         <v>2</v>
       </c>
@@ -3241,7 +3292,11 @@
           <t>屈折、調節の異常</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>近視</t>
+        </is>
+      </c>
       <c r="H31" t="n">
         <v>1</v>
       </c>
@@ -3333,7 +3388,11 @@
           <t>屈折、調節の矯正</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>眼鏡レンズ</t>
+        </is>
+      </c>
       <c r="H32" t="n">
         <v>3</v>
       </c>
@@ -3431,7 +3490,6 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
         <v>2</v>
       </c>
@@ -3523,7 +3581,6 @@
           <t>外眼筋の作用と眼球運動</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
         <v>3</v>
       </c>
@@ -3615,7 +3672,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>麻痺性斜視</t>
+        </is>
+      </c>
       <c r="H35" t="n">
         <v>2</v>
       </c>
@@ -3713,7 +3774,6 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
         <v>1</v>
       </c>
@@ -3805,7 +3865,6 @@
           <t>緑内障</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
         <v>3</v>
       </c>
@@ -3899,7 +3958,6 @@
           <t>視能検査機器の基本的知識</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
         <v>2</v>
       </c>
@@ -3991,7 +4049,11 @@
           <t>涙液検査</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Schirmer試験</t>
+        </is>
+      </c>
       <c r="H39" t="n">
         <v>1</v>
       </c>
@@ -4083,7 +4145,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>視覚生理学</t>
+        </is>
+      </c>
       <c r="H40" t="n">
         <v>1</v>
       </c>
@@ -4175,7 +4241,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>回旋斜視</t>
+        </is>
+      </c>
       <c r="H41" t="n">
         <v>1</v>
       </c>
@@ -4267,7 +4337,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>視覚生理学</t>
+        </is>
+      </c>
       <c r="H42" t="n">
         <v>3</v>
       </c>
@@ -4359,7 +4433,6 @@
           <t>身体症状症&lt;心因性視能障害&gt;</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
         <v>2</v>
       </c>
@@ -4451,7 +4524,6 @@
           <t>公衆衛生総論</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
         <v>1</v>
       </c>
@@ -4543,7 +4615,11 @@
           <t>眼瞼</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>麦粒腫</t>
+        </is>
+      </c>
       <c r="H45" t="n">
         <v>1</v>
       </c>
@@ -4635,7 +4711,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
         <v>1</v>
       </c>
@@ -4727,7 +4802,11 @@
           <t>医療の質と安全の確保</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>患者の安全管理</t>
+        </is>
+      </c>
       <c r="H47" t="n">
         <v>2</v>
       </c>
@@ -4819,7 +4898,6 @@
           <t>屈折異常</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
         <v>1</v>
       </c>
@@ -4911,7 +4989,6 @@
           <t>網膜</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
       <c r="H49" t="n">
         <v>1</v>
       </c>
@@ -5003,7 +5080,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>外斜視</t>
+        </is>
+      </c>
       <c r="H50" t="n">
         <v>3</v>
       </c>
@@ -5095,7 +5176,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>内斜視</t>
+        </is>
+      </c>
       <c r="H51" t="n">
         <v>1</v>
       </c>
@@ -5187,7 +5272,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>不同視弱視</t>
+        </is>
+      </c>
       <c r="H52" t="n">
         <v>1</v>
       </c>
@@ -5279,7 +5368,11 @@
           <t>眼球運動</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>神経筋接合部障害</t>
+        </is>
+      </c>
       <c r="H53" t="n">
         <v>3</v>
       </c>
@@ -5371,7 +5464,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>上下斜視</t>
+        </is>
+      </c>
       <c r="H54" t="n">
         <v>1</v>
       </c>
@@ -5463,7 +5560,6 @@
           <t>定義</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
       <c r="H55" t="n">
         <v>3</v>
       </c>
@@ -5555,7 +5651,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>交代性上斜位</t>
+        </is>
+      </c>
       <c r="H56" t="n">
         <v>1</v>
       </c>
@@ -5647,7 +5747,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>内斜視</t>
+        </is>
+      </c>
       <c r="H57" t="n">
         <v>1</v>
       </c>
@@ -5739,7 +5843,11 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>遮閉法</t>
+        </is>
+      </c>
       <c r="H58" t="n">
         <v>2</v>
       </c>
@@ -5831,7 +5939,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>不同視弱視</t>
+        </is>
+      </c>
       <c r="H59" t="n">
         <v>4</v>
       </c>
@@ -5923,7 +6035,6 @@
           <t>患者と視能訓練士の関係</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
       <c r="H60" t="n">
         <v>1</v>
       </c>
@@ -6015,7 +6126,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>形態覚遮断弱視</t>
+        </is>
+      </c>
       <c r="H61" t="n">
         <v>1</v>
       </c>
@@ -6107,7 +6222,6 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
       <c r="H62" t="n">
         <v>1</v>
       </c>
@@ -6199,7 +6313,6 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
       <c r="H63" t="n">
         <v>1</v>
       </c>
@@ -6291,7 +6404,6 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
       <c r="H64" t="n">
         <v>3</v>
       </c>
@@ -6383,7 +6495,11 @@
           <t>眼窩</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>眼球突出、陥凹</t>
+        </is>
+      </c>
       <c r="H65" t="n">
         <v>1</v>
       </c>
@@ -6475,7 +6591,6 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
       <c r="H66" t="n">
         <v>1</v>
       </c>
@@ -6567,7 +6682,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>麻痺性斜視</t>
+        </is>
+      </c>
       <c r="H67" t="n">
         <v>2</v>
       </c>
@@ -6665,7 +6784,6 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
       <c r="H68" t="n">
         <v>2</v>
       </c>
@@ -6758,7 +6876,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>視覚生理学</t>
+        </is>
+      </c>
       <c r="H69" t="n">
         <v>3</v>
       </c>
@@ -6851,7 +6973,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>麻痺性斜視</t>
+        </is>
+      </c>
       <c r="H70" t="n">
         <v>2</v>
       </c>
@@ -6944,7 +7070,6 @@
           <t>眼底検査</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
       <c r="H71" t="n">
         <v>4</v>
       </c>
@@ -7042,7 +7167,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>視覚生理学</t>
+        </is>
+      </c>
       <c r="H72" t="n">
         <v>4</v>
       </c>
@@ -7140,7 +7269,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
       <c r="H73" t="n">
         <v>4</v>
       </c>
@@ -7238,7 +7366,6 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
       <c r="H74" t="n">
         <v>4</v>
       </c>
@@ -7336,7 +7463,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
       <c r="H75" t="n">
         <v>4</v>
       </c>
@@ -7434,7 +7560,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>麻痺性斜視</t>
+        </is>
+      </c>
       <c r="H76" t="n">
         <v>2</v>
       </c>
@@ -7527,7 +7657,11 @@
           <t>加齢、老化</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>加齢による細胞と組織の変化</t>
+        </is>
+      </c>
       <c r="H77" t="n">
         <v>1</v>
       </c>
@@ -7619,7 +7753,11 @@
           <t>末梢神経の構造と機能</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>脳神経（第Ⅰ〜Ⅻ脳神経）</t>
+        </is>
+      </c>
       <c r="H78" t="n">
         <v>1</v>
       </c>
@@ -7711,7 +7849,6 @@
           <t>心臓、血管の構造と機能</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
       <c r="H79" t="n">
         <v>1</v>
       </c>
@@ -7803,7 +7940,11 @@
           <t>眼球</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>水晶体</t>
+        </is>
+      </c>
       <c r="H80" t="n">
         <v>1</v>
       </c>
@@ -7895,7 +8036,11 @@
           <t>新生児期、乳児期</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>新生児、乳児の生理</t>
+        </is>
+      </c>
       <c r="H81" t="n">
         <v>1</v>
       </c>
@@ -7987,7 +8132,6 @@
           <t>視能検査機器の基本的知識</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
       <c r="H82" t="n">
         <v>1</v>
       </c>
@@ -8079,7 +8223,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>上下斜視</t>
+        </is>
+      </c>
       <c r="H83" t="n">
         <v>3</v>
       </c>
@@ -8171,7 +8319,6 @@
           <t>保健、医療、福祉、介護制度</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
       <c r="H84" t="n">
         <v>1</v>
       </c>
@@ -8263,7 +8410,6 @@
           <t>視能検査機器の基本的知識</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
       <c r="H85" t="n">
         <v>1</v>
       </c>
@@ -8355,7 +8501,11 @@
           <t>薬物の副作用</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>眼科で用いられる薬物の副作用</t>
+        </is>
+      </c>
       <c r="H86" t="n">
         <v>1</v>
       </c>
@@ -8447,7 +8597,11 @@
           <t>両眼視</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>定義と正常、異常</t>
+        </is>
+      </c>
       <c r="H87" t="n">
         <v>2</v>
       </c>
@@ -8545,7 +8699,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>視覚生理学</t>
+        </is>
+      </c>
       <c r="H88" t="n">
         <v>1</v>
       </c>
@@ -8637,7 +8795,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>視覚の閾値</t>
+        </is>
+      </c>
       <c r="H89" t="n">
         <v>1</v>
       </c>
@@ -8729,7 +8891,6 @@
           <t>視能検査機器の基本的知識</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
       <c r="H90" t="n">
         <v>3</v>
       </c>
@@ -8821,7 +8982,11 @@
           <t>外眼筋の作用と眼球運動</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>外眼筋の単独作用</t>
+        </is>
+      </c>
       <c r="H91" t="n">
         <v>1</v>
       </c>
@@ -8913,7 +9078,11 @@
           <t>外眼筋の作用と眼球運動</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>外眼筋の単独作用</t>
+        </is>
+      </c>
       <c r="H92" t="n">
         <v>1</v>
       </c>
@@ -9005,7 +9174,11 @@
           <t>両眼視</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>定義と正常、異常</t>
+        </is>
+      </c>
       <c r="H93" t="n">
         <v>1</v>
       </c>
@@ -9097,7 +9270,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>回旋斜視</t>
+        </is>
+      </c>
       <c r="H94" t="n">
         <v>2</v>
       </c>
@@ -9195,7 +9372,11 @@
           <t>外眼筋の作用と眼球運動</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>外眼筋の単独作用</t>
+        </is>
+      </c>
       <c r="H95" t="n">
         <v>2</v>
       </c>
@@ -9287,7 +9468,11 @@
           <t>輻湊、開散と屈折、調節</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>定義</t>
+        </is>
+      </c>
       <c r="H96" t="n">
         <v>3</v>
       </c>
@@ -9379,7 +9564,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>視覚の閾値</t>
+        </is>
+      </c>
       <c r="H97" t="n">
         <v>2</v>
       </c>
@@ -9471,7 +9660,6 @@
           <t>外眼筋の作用と眼球運動</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
       <c r="H98" t="n">
         <v>1</v>
       </c>
@@ -9563,7 +9751,6 @@
           <t>基本的知識</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
       <c r="H99" t="n">
         <v>2</v>
       </c>
@@ -9655,7 +9842,11 @@
           <t>角膜検査</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>角膜内皮細胞検査</t>
+        </is>
+      </c>
       <c r="H100" t="n">
         <v>2</v>
       </c>
@@ -9747,7 +9938,6 @@
           <t>視力検査</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
       <c r="H101" t="n">
         <v>2</v>
       </c>
@@ -9845,7 +10035,6 @@
           <t>眼圧検査</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr"/>
       <c r="H102" t="n">
         <v>1</v>
       </c>
@@ -9937,7 +10126,11 @@
           <t>画像検査</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr"/>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>光干渉断層計〈OCT〉</t>
+        </is>
+      </c>
       <c r="H103" t="n">
         <v>2</v>
       </c>
@@ -10035,7 +10228,11 @@
           <t>涙液検査</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr"/>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>生体染色検査</t>
+        </is>
+      </c>
       <c r="H104" t="n">
         <v>3</v>
       </c>
@@ -10133,7 +10330,11 @@
           <t>前眼部、透光体検査</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr"/>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>細隙灯顕微鏡検査</t>
+        </is>
+      </c>
       <c r="H105" t="n">
         <v>2</v>
       </c>
@@ -10225,7 +10426,11 @@
           <t>涙液検査</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr"/>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Schirmer試験</t>
+        </is>
+      </c>
       <c r="H106" t="n">
         <v>1</v>
       </c>
@@ -10317,7 +10522,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr"/>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>形態覚遮断弱視</t>
+        </is>
+      </c>
       <c r="H107" t="n">
         <v>1</v>
       </c>
@@ -10409,7 +10618,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr"/>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>視覚生理学</t>
+        </is>
+      </c>
       <c r="H108" t="n">
         <v>1</v>
       </c>
@@ -10501,7 +10714,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr"/>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>視覚の成り立ち</t>
+        </is>
+      </c>
       <c r="H109" t="n">
         <v>1</v>
       </c>
@@ -10593,7 +10810,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr"/>
       <c r="H110" t="n">
         <v>1</v>
       </c>
@@ -10685,7 +10901,11 @@
           <t>屈折、調節の異常</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr"/>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>老視</t>
+        </is>
+      </c>
       <c r="H111" t="n">
         <v>2</v>
       </c>
@@ -10777,7 +10997,6 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr"/>
       <c r="H112" t="n">
         <v>2</v>
       </c>
@@ -10875,7 +11094,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr"/>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>視覚の成り立ち</t>
+        </is>
+      </c>
       <c r="H113" t="n">
         <v>1</v>
       </c>
@@ -10967,7 +11190,6 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr"/>
       <c r="H114" t="n">
         <v>1</v>
       </c>
@@ -11059,7 +11281,6 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr"/>
       <c r="H115" t="n">
         <v>2</v>
       </c>
@@ -11151,7 +11372,11 @@
           <t>輻湊、開散と屈折、調節</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr"/>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>定義</t>
+        </is>
+      </c>
       <c r="H116" t="n">
         <v>3</v>
       </c>
@@ -11243,7 +11468,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr"/>
       <c r="H117" t="n">
         <v>1</v>
       </c>
@@ -11335,7 +11559,11 @@
           <t>ぶどう膜</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr"/>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>ぶどう膜炎</t>
+        </is>
+      </c>
       <c r="H118" t="n">
         <v>3</v>
       </c>
@@ -11427,7 +11655,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr"/>
       <c r="H119" t="n">
         <v>1</v>
       </c>
@@ -11519,7 +11746,11 @@
           <t>網膜</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr"/>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>中心性漿液性脈絡網膜症</t>
+        </is>
+      </c>
       <c r="H120" t="n">
         <v>3</v>
       </c>
@@ -11611,7 +11842,11 @@
           <t>水晶体</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr"/>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>水晶体偏位、脱臼</t>
+        </is>
+      </c>
       <c r="H121" t="n">
         <v>1</v>
       </c>
@@ -11703,7 +11938,11 @@
           <t>強膜</t>
         </is>
       </c>
-      <c r="G122" t="inlineStr"/>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>強膜炎</t>
+        </is>
+      </c>
       <c r="H122" t="n">
         <v>1</v>
       </c>
@@ -11795,7 +12034,11 @@
           <t>角膜</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr"/>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>円錐角膜</t>
+        </is>
+      </c>
       <c r="H123" t="n">
         <v>1</v>
       </c>
@@ -11887,7 +12130,11 @@
           <t>結膜</t>
         </is>
       </c>
-      <c r="G124" t="inlineStr"/>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>結膜炎</t>
+        </is>
+      </c>
       <c r="H124" t="n">
         <v>1</v>
       </c>
@@ -11979,7 +12226,11 @@
           <t>水晶体</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr"/>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>白内障</t>
+        </is>
+      </c>
       <c r="H125" t="n">
         <v>1</v>
       </c>
@@ -12071,7 +12322,11 @@
           <t>緑内障</t>
         </is>
       </c>
-      <c r="G126" t="inlineStr"/>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>正常眼圧緑内障</t>
+        </is>
+      </c>
       <c r="H126" t="n">
         <v>1</v>
       </c>
@@ -12163,7 +12418,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr"/>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>内斜視</t>
+        </is>
+      </c>
       <c r="H127" t="n">
         <v>3</v>
       </c>
@@ -12255,7 +12514,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G128" t="inlineStr"/>
       <c r="H128" t="n">
         <v>1</v>
       </c>
@@ -12347,7 +12605,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G129" t="inlineStr"/>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>内斜視</t>
+        </is>
+      </c>
       <c r="H129" t="n">
         <v>1</v>
       </c>
@@ -12439,7 +12701,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr"/>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>外斜視</t>
+        </is>
+      </c>
       <c r="H130" t="n">
         <v>1</v>
       </c>
@@ -12531,7 +12797,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr"/>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>麻痺性斜視</t>
+        </is>
+      </c>
       <c r="H131" t="n">
         <v>1</v>
       </c>
@@ -12623,7 +12893,11 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G132" t="inlineStr"/>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>屈折矯正</t>
+        </is>
+      </c>
       <c r="H132" t="n">
         <v>1</v>
       </c>
@@ -12715,7 +12989,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G133" t="inlineStr"/>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>内斜視</t>
+        </is>
+      </c>
       <c r="H133" t="n">
         <v>2</v>
       </c>
@@ -12807,7 +13085,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G134" t="inlineStr"/>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>微小斜視</t>
+        </is>
+      </c>
       <c r="H134" t="n">
         <v>3</v>
       </c>
@@ -12899,7 +13181,11 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G135" t="inlineStr"/>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>遮閉法</t>
+        </is>
+      </c>
       <c r="H135" t="n">
         <v>1</v>
       </c>
@@ -12991,7 +13277,6 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G136" t="inlineStr"/>
       <c r="H136" t="n">
         <v>3</v>
       </c>
@@ -13083,7 +13368,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G137" t="inlineStr"/>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>A-V型斜視</t>
+        </is>
+      </c>
       <c r="H137" t="n">
         <v>1</v>
       </c>
@@ -13175,7 +13464,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G138" t="inlineStr"/>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>形態覚遮断弱視</t>
+        </is>
+      </c>
       <c r="H138" t="n">
         <v>1</v>
       </c>
@@ -13267,7 +13560,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G139" t="inlineStr"/>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>不同視弱視</t>
+        </is>
+      </c>
       <c r="H139" t="n">
         <v>2</v>
       </c>
@@ -13359,7 +13656,6 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G140" t="inlineStr"/>
       <c r="H140" t="n">
         <v>3</v>
       </c>
@@ -13451,7 +13747,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G141" t="inlineStr"/>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>斜視特殊型</t>
+        </is>
+      </c>
       <c r="H141" t="n">
         <v>3</v>
       </c>
@@ -13543,7 +13843,11 @@
           <t>生理光学の基礎知識</t>
         </is>
       </c>
-      <c r="G142" t="inlineStr"/>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>レンズ</t>
+        </is>
+      </c>
       <c r="H142" t="n">
         <v>4</v>
       </c>
@@ -13641,7 +13945,11 @@
           <t>両眼視</t>
         </is>
       </c>
-      <c r="G143" t="inlineStr"/>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>定義と正常、異常</t>
+        </is>
+      </c>
       <c r="H143" t="n">
         <v>4</v>
       </c>
@@ -13739,7 +14047,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G144" t="inlineStr"/>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>麻痺性斜視</t>
+        </is>
+      </c>
       <c r="H144" t="n">
         <v>2</v>
       </c>
@@ -13837,7 +14149,11 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G145" t="inlineStr"/>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>うっ血乳頭</t>
+        </is>
+      </c>
       <c r="H145" t="n">
         <v>3</v>
       </c>
@@ -13935,7 +14251,6 @@
           <t>屈折、調節の異常</t>
         </is>
       </c>
-      <c r="G146" t="inlineStr"/>
       <c r="H146" t="n">
         <v>4</v>
       </c>
@@ -14028,7 +14343,11 @@
           <t>眼窩</t>
         </is>
       </c>
-      <c r="G147" t="inlineStr"/>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>眼球突出、陥凹</t>
+        </is>
+      </c>
       <c r="H147" t="n">
         <v>4</v>
       </c>
@@ -14126,7 +14445,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G148" t="inlineStr"/>
       <c r="H148" t="n">
         <v>3</v>
       </c>
@@ -14224,7 +14542,6 @@
           <t>定義</t>
         </is>
       </c>
-      <c r="G149" t="inlineStr"/>
       <c r="H149" t="n">
         <v>4</v>
       </c>
@@ -14317,7 +14634,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G150" t="inlineStr"/>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>内斜視</t>
+        </is>
+      </c>
       <c r="H150" t="n">
         <v>4</v>
       </c>
@@ -14415,7 +14736,6 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G151" t="inlineStr"/>
       <c r="H151" t="n">
         <v>3</v>
       </c>

--- a/CO国試data/CO_questions_2024.xlsx
+++ b/CO国試data/CO_questions_2024.xlsx
@@ -598,10 +598,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S2" t="b">
+        <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -694,10 +692,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S3" t="b">
+        <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -886,10 +882,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S5" t="b">
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1073,10 +1067,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S7" t="b">
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1255,10 +1247,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S9" t="b">
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1447,10 +1437,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S11" t="b">
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1544,10 +1532,8 @@
           <t>2024_co_24_am011.jpg</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S12" t="b">
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1640,10 +1626,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S13" t="b">
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1737,10 +1721,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S14" t="b">
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1839,10 +1821,8 @@
           <t>2024_co_24_am014.jpg</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S15" t="b">
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1935,10 +1915,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S16" t="b">
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2026,10 +2004,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S17" t="b">
+        <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2123,10 +2099,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S18" t="b">
+        <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2225,10 +2199,8 @@
           <t>2024_co_24_am018.jpg</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S19" t="b">
+        <v>0</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2316,10 +2288,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S20" t="b">
+        <v>0</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2407,10 +2377,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S21" t="b">
+        <v>0</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2503,10 +2471,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S22" t="b">
+        <v>0</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2600,10 +2566,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S23" t="b">
+        <v>0</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2691,10 +2655,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S24" t="b">
+        <v>0</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2787,10 +2749,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S25" t="b">
+        <v>0</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -2969,10 +2929,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S27" t="b">
+        <v>0</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3061,10 +3019,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S28" t="b">
+        <v>0</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3157,10 +3113,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S29" t="b">
+        <v>0</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3249,10 +3203,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S30" t="b">
+        <v>0</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3345,10 +3297,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S31" t="b">
+        <v>0</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3447,10 +3397,8 @@
           <t>2024_co_24_am031.jpg</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S32" t="b">
+        <v>0</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3538,10 +3486,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S33" t="b">
+        <v>0</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3731,10 +3677,8 @@
           <t>2024_co_24_am034.jpg</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S35" t="b">
+        <v>0</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -3822,10 +3766,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S36" t="b">
+        <v>0</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -3915,10 +3857,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S37" t="b">
+        <v>0</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4006,10 +3946,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S38" t="b">
+        <v>0</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4102,10 +4040,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S39" t="b">
+        <v>0</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4198,10 +4134,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S40" t="b">
+        <v>0</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4294,10 +4228,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S41" t="b">
+        <v>0</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4481,10 +4413,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S43" t="b">
+        <v>0</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4572,10 +4502,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S44" t="b">
+        <v>0</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4668,10 +4596,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S45" t="b">
+        <v>0</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -4759,10 +4685,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S46" t="b">
+        <v>0</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -4855,10 +4779,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S47" t="b">
+        <v>0</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -4946,10 +4868,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S48" t="b">
+        <v>0</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5037,10 +4957,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S49" t="b">
+        <v>0</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5229,10 +5147,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S51" t="b">
+        <v>0</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5325,10 +5241,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S52" t="b">
+        <v>0</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5517,10 +5431,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S54" t="b">
+        <v>0</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -5704,10 +5616,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S56" t="b">
+        <v>0</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -5800,10 +5710,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S57" t="b">
+        <v>0</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -5896,10 +5804,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S58" t="b">
+        <v>0</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -5992,10 +5898,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S59" t="b">
+        <v>0</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6083,10 +5987,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S60" t="b">
+        <v>0</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6179,10 +6081,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S61" t="b">
+        <v>0</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6270,10 +6170,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S62" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S62" t="b">
+        <v>0</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6361,10 +6259,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S63" t="b">
+        <v>0</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6548,10 +6444,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S65" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S65" t="b">
+        <v>0</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -6639,10 +6533,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S66" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S66" t="b">
+        <v>0</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -6741,10 +6633,8 @@
           <t>2024_co_24_am066.jpg;2024_co_24_am066_2.jpg;2024_co_24_am066_3.jpg;2024_co_24_am066_4.jpg;2024_co_24_am066_5.jpg;2024_co_24_am066_6.jpg</t>
         </is>
       </c>
-      <c r="S67" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S67" t="b">
+        <v>0</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -6833,10 +6723,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S68" t="b">
+        <v>0</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -6930,10 +6818,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S69" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S69" t="b">
+        <v>0</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7027,10 +6913,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S70" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S70" t="b">
+        <v>0</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7124,10 +7008,8 @@
           <t>2024_co_24_am070.jpg</t>
         </is>
       </c>
-      <c r="S71" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S71" t="b">
+        <v>0</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7226,10 +7108,8 @@
           <t>2024_co_24_am071.jpg</t>
         </is>
       </c>
-      <c r="S72" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S72" t="b">
+        <v>0</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7323,10 +7203,8 @@
           <t>2024_co_24_am072.jpg</t>
         </is>
       </c>
-      <c r="S73" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S73" t="b">
+        <v>0</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -7420,10 +7298,8 @@
           <t>2024_co_24_am073.jpg</t>
         </is>
       </c>
-      <c r="S74" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S74" t="b">
+        <v>0</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -7517,10 +7393,8 @@
           <t>2024_co_24_am074.jpg</t>
         </is>
       </c>
-      <c r="S75" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S75" t="b">
+        <v>0</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -7614,10 +7488,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S76" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S76" t="b">
+        <v>0</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -7710,10 +7582,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S77" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S77" t="b">
+        <v>0</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -7806,10 +7676,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S78" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S78" t="b">
+        <v>0</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -7897,10 +7765,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S79" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S79" t="b">
+        <v>0</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -7993,10 +7859,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S80" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S80" t="b">
+        <v>0</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8089,10 +7953,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S81" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S81" t="b">
+        <v>0</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8180,10 +8042,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S82" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S82" t="b">
+        <v>0</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8367,10 +8227,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S84" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S84" t="b">
+        <v>0</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -8458,10 +8316,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S85" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S85" t="b">
+        <v>0</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -8554,10 +8410,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S86" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S86" t="b">
+        <v>0</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -8656,10 +8510,8 @@
           <t>2024_co_24_pm011.jpg</t>
         </is>
       </c>
-      <c r="S87" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S87" t="b">
+        <v>0</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -8752,10 +8604,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S88" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S88" t="b">
+        <v>0</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -8848,10 +8698,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S89" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S89" t="b">
+        <v>0</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -8939,10 +8787,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S90" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S90" t="b">
+        <v>0</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9035,10 +8881,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S91" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S91" t="b">
+        <v>0</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9131,10 +8975,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S92" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S92" t="b">
+        <v>0</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -9227,10 +9069,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S93" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S93" t="b">
+        <v>0</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -9329,10 +9169,8 @@
           <t>2024_co_24_pm018.jpg</t>
         </is>
       </c>
-      <c r="S94" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S94" t="b">
+        <v>0</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -9425,10 +9263,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S95" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S95" t="b">
+        <v>0</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -9617,10 +9453,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S97" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S97" t="b">
+        <v>0</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -9708,10 +9542,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S98" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S98" t="b">
+        <v>0</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -9799,10 +9631,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S99" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S99" t="b">
+        <v>0</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -9895,10 +9725,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S100" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S100" t="b">
+        <v>0</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -9992,10 +9820,8 @@
           <t>2024_co_24_pm025.jpg</t>
         </is>
       </c>
-      <c r="S101" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S101" t="b">
+        <v>0</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -10083,10 +9909,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S102" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S102" t="b">
+        <v>0</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -10185,10 +10009,8 @@
           <t>2024_co_24_pm027.jpg</t>
         </is>
       </c>
-      <c r="S103" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S103" t="b">
+        <v>0</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -10383,10 +10205,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S105" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S105" t="b">
+        <v>0</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -10479,10 +10299,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S106" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S106" t="b">
+        <v>0</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -10575,10 +10393,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S107" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S107" t="b">
+        <v>0</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -10671,10 +10487,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S108" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S108" t="b">
+        <v>0</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -10767,10 +10581,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S109" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S109" t="b">
+        <v>0</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -10858,10 +10670,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S110" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S110" t="b">
+        <v>0</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -10954,10 +10764,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S111" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S111" t="b">
+        <v>0</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -11051,10 +10859,8 @@
           <t>2024_co_24_pm036.jpg;2024_co_24_pm036_2.jpg;2024_co_24_pm036_3.jpg;2024_co_24_pm036_4.jpg;2024_co_24_pm036_5.jpg</t>
         </is>
       </c>
-      <c r="S112" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S112" t="b">
+        <v>0</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -11147,10 +10953,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S113" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S113" t="b">
+        <v>0</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -11238,10 +11042,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S114" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S114" t="b">
+        <v>0</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -11329,10 +11131,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S115" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S115" t="b">
+        <v>0</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -11516,10 +11316,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S117" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S117" t="b">
+        <v>0</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -11703,10 +11501,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S119" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S119" t="b">
+        <v>0</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -11895,10 +11691,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S121" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S121" t="b">
+        <v>0</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -11991,10 +11785,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S122" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S122" t="b">
+        <v>0</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -12087,10 +11879,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S123" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S123" t="b">
+        <v>0</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -12183,10 +11973,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S124" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S124" t="b">
+        <v>0</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -12279,10 +12067,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S125" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S125" t="b">
+        <v>0</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -12375,10 +12161,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S126" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S126" t="b">
+        <v>0</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -12562,10 +12346,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S128" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S128" t="b">
+        <v>0</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -12658,10 +12440,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S129" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S129" t="b">
+        <v>0</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -12754,10 +12534,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S130" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S130" t="b">
+        <v>0</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -12850,10 +12628,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S131" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S131" t="b">
+        <v>0</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -12946,10 +12722,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S132" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S132" t="b">
+        <v>0</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -13042,10 +12816,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S133" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S133" t="b">
+        <v>0</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -13234,10 +13006,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S135" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S135" t="b">
+        <v>0</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -13421,10 +13191,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S137" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S137" t="b">
+        <v>0</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -13517,10 +13285,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S138" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S138" t="b">
+        <v>0</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -13613,10 +13379,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S139" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S139" t="b">
+        <v>0</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -13902,10 +13666,8 @@
           <t>2024_co_24_pm066.jpg</t>
         </is>
       </c>
-      <c r="S142" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S142" t="b">
+        <v>0</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -14004,10 +13766,8 @@
           <t>2024_co_24_pm067.jpg</t>
         </is>
       </c>
-      <c r="S143" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S143" t="b">
+        <v>0</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -14106,10 +13866,8 @@
           <t>2024_co_24_pm068.jpg</t>
         </is>
       </c>
-      <c r="S144" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S144" t="b">
+        <v>0</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -14208,10 +13966,8 @@
           <t>2024_co_24_pm069.jpg</t>
         </is>
       </c>
-      <c r="S145" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S145" t="b">
+        <v>0</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -14300,10 +14056,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S146" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S146" t="b">
+        <v>0</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -14402,10 +14156,8 @@
           <t>2024_co_24_pm071.jpg</t>
         </is>
       </c>
-      <c r="S147" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S147" t="b">
+        <v>0</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -14499,10 +14251,8 @@
           <t>2024_co_24_pm072.jpg</t>
         </is>
       </c>
-      <c r="S148" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S148" t="b">
+        <v>0</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -14591,10 +14341,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S149" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S149" t="b">
+        <v>0</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -14693,10 +14441,8 @@
           <t>2024_co_24_pm074.jpg</t>
         </is>
       </c>
-      <c r="S150" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S150" t="b">
+        <v>0</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -14785,10 +14531,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S151" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S151" t="b">
+        <v>0</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>

--- a/CO国試data/CO_questions_2024.xlsx
+++ b/CO国試data/CO_questions_2024.xlsx
@@ -773,7 +773,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>BC</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -786,10 +786,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S4" t="b">
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -958,7 +956,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -971,10 +969,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S6" t="b">
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1143,7 +1139,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1156,10 +1152,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S8" t="b">
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1328,7 +1322,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1341,10 +1335,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S10" t="b">
+        <v>1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2825,7 +2817,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -2838,10 +2830,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S26" t="b">
+        <v>1</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3562,7 +3552,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -3575,10 +3565,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S34" t="b">
+        <v>1</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4309,7 +4297,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CD</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -4322,10 +4310,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S42" t="b">
+        <v>1</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5038,7 +5024,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5051,10 +5037,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S50" t="b">
+        <v>1</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5322,7 +5306,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CD</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -5335,10 +5319,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S53" t="b">
+        <v>1</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5507,7 +5489,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -5520,10 +5502,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S55" t="b">
+        <v>1</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6335,7 +6315,7 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>BC</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -6348,10 +6328,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S64" t="b">
+        <v>1</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8123,7 +8101,7 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>BC</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -8136,10 +8114,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S83" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S83" t="b">
+        <v>1</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9344,7 +9320,7 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
@@ -9357,10 +9333,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S96" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S96" t="b">
+        <v>1</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10091,7 +10065,7 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>BC</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
@@ -10109,10 +10083,8 @@
           <t>2024_co_24_pm028.jpg</t>
         </is>
       </c>
-      <c r="S104" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S104" t="b">
+        <v>1</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11212,7 +11184,7 @@
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
@@ -11225,10 +11197,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S116" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S116" t="b">
+        <v>1</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -11397,7 +11367,7 @@
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
@@ -11410,10 +11380,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S118" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S118" t="b">
+        <v>1</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -11582,7 +11550,7 @@
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
@@ -11595,10 +11563,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S120" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S120" t="b">
+        <v>1</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -12242,7 +12208,7 @@
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
@@ -12255,10 +12221,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S127" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S127" t="b">
+        <v>1</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -12333,7 +12297,7 @@
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>ABCDE</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
@@ -12347,7 +12311,7 @@
         </is>
       </c>
       <c r="S128" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -12897,7 +12861,7 @@
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
@@ -12910,10 +12874,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S134" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S134" t="b">
+        <v>1</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -13082,7 +13044,7 @@
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="P136" t="inlineStr">
@@ -13095,10 +13057,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S136" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S136" t="b">
+        <v>1</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -13455,7 +13415,7 @@
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
@@ -13468,10 +13428,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S140" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S140" t="b">
+        <v>1</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -13551,7 +13509,7 @@
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CD</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
@@ -13564,10 +13522,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S141" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S141" t="b">
+        <v>1</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
